--- a/artfynd/S 558-2022 artfynd.xlsx
+++ b/artfynd/S 558-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56126519</v>
+        <v>137376319</v>
       </c>
       <c r="B2" t="n">
-        <v>56895</v>
+        <v>57971</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100088</v>
+        <v>100082</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,44 +708,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Våksjöbäcken, Sm</t>
+          <t>Högerås, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559224</v>
+        <v>559108</v>
       </c>
       <c r="R2" t="n">
-        <v>6303489</v>
+        <v>6303239</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -769,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-06-04</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-06-04</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,42 +762,387 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Intill bäcken, 30-årig blandskog</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Karin Agstam-Norlin</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Jonatan Strandberg</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Jonatan Strandberg, Moa Berglund</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137376319</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>56126519</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56895</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100088</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vanlig snok</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Natrix natrix</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Våksjöbäcken, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>559224</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6303489</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Kristvalla</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2015-06-04</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2015-06-04</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Intill bäcken, 30-årig blandskog</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Karin Agstam-Norlin</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Sofia Lundman</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Via Sofia Lundman</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr">
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/56126519</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>137376316</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98274</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Högerås, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>559167</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6303177</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kristvalla</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jonatan Strandberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jonatan Strandberg, Moa Berglund</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137376316</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137376317</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100072</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222306</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Stjärnstarr</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Carex echinata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Murray</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Högerås, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>559161</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6303180</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kristvalla</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jonatan Strandberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jonatan Strandberg, Moa Berglund</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137376317</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 558-2022 artfynd.xlsx
+++ b/artfynd/S 558-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137376319</v>
       </c>
       <c r="B2" t="n">
-        <v>57971</v>
+        <v>57972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>137376316</v>
       </c>
       <c r="B4" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>137376317</v>
       </c>
       <c r="B5" t="n">
-        <v>100072</v>
+        <v>100078</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 558-2022 artfynd.xlsx
+++ b/artfynd/S 558-2022 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>137376316</v>
       </c>
       <c r="B4" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>137376317</v>
       </c>
       <c r="B5" t="n">
-        <v>100078</v>
+        <v>100090</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 558-2022 artfynd.xlsx
+++ b/artfynd/S 558-2022 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>137376316</v>
       </c>
       <c r="B4" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>137376317</v>
       </c>
       <c r="B5" t="n">
-        <v>100090</v>
+        <v>100091</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 558-2022 artfynd.xlsx
+++ b/artfynd/S 558-2022 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>137376316</v>
       </c>
       <c r="B4" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>137376317</v>
       </c>
       <c r="B5" t="n">
-        <v>100091</v>
+        <v>100094</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 558-2022 artfynd.xlsx
+++ b/artfynd/S 558-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137376319</v>
       </c>
       <c r="B2" t="n">
-        <v>57972</v>
+        <v>57975</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>137376316</v>
       </c>
       <c r="B4" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>137376317</v>
       </c>
       <c r="B5" t="n">
-        <v>100094</v>
+        <v>100098</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
